--- a/AAII_Financials/Quarterly/RIVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RIVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>RIVN</t>
   </si>
@@ -656,185 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1658000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1381000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1286000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1558000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1303000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1240000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1734000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>874000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1158000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1204000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1315000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1337000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1121000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>661000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>663000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>536000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>364000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>95000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>54000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>4</v>
       </c>
@@ -850,77 +853,80 @@
       <c r="AB8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1262000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1166000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1534000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1509000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1034000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1564000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1266000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1609000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1731000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1921000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1814000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1533000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1196000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1777000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1058000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>955000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>409000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>437000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>83000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
@@ -942,71 +948,74 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E10" s="3">
         <v>119000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>120000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-206000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>206000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>170000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-392000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-451000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-527000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-606000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-477000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-412000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-535000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1114000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-522000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-591000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-314000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-383000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-82000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1028,8 +1037,11 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1060,94 +1072,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E12" s="3">
         <v>458000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>424000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>453000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>410000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>381000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>374000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>350000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>428000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>461000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>526000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>529000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>444000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>496000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>373000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>421000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>543000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>547000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>726000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>441000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>394000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>289000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>255000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>220000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>151000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>141000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>103000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1232,22 +1248,25 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>-506000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>183000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
@@ -1256,14 +1275,14 @@
         <v>-101000</v>
       </c>
       <c r="J14" s="3">
+        <v>82000</v>
+      </c>
+      <c r="K14" s="3">
         <v>123000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>90000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1276,101 +1295,104 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>-114000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>395000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>113000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>188000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-17000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>458000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E15" s="3">
         <v>194000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>201000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>187000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>196000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>200000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>218000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>259000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>274000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>280000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>270000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>256000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>223000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>188000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>53000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>52000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1386,8 +1408,8 @@
       <c r="X15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1404,8 +1426,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1433,157 +1458,161 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2494000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2262000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2119000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2541000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2417000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1895000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2395000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2043000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2533000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2688000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2896000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2777000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2406000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2094000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2458000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2310000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2072000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1674000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2491000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1235000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>580000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>410000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>353000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>288000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>199000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>182000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>138000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-836000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-881000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-833000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-983000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1114000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-655000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-661000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1169000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1375000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1484000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1581000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1440000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1285000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1433000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1795000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1774000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1708000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1579000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2437000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1234000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1599,14 +1628,17 @@
       <c r="AB18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-138000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-110000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1637,37 +1669,38 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-478000</v>
+        <v>-18000</v>
       </c>
       <c r="E20" s="3">
-        <v>-32000</v>
+        <v>28000</v>
       </c>
       <c r="F20" s="3">
-        <v>191000</v>
+        <v>151000</v>
       </c>
       <c r="G20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-107000</v>
-      </c>
       <c r="I20" s="3">
-        <v>182000</v>
+        <v>-6000</v>
       </c>
       <c r="J20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-184000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2000</v>
       </c>
       <c r="M20" s="3">
         <v>-2000</v>
@@ -1676,32 +1709,32 @@
         <v>-2000</v>
       </c>
       <c r="O20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>105000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>75000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>23000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1717,77 +1750,80 @@
       <c r="AB20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-209000</v>
+        <v>-581000</v>
       </c>
       <c r="E21" s="3">
-        <v>-600000</v>
+        <v>-715000</v>
       </c>
       <c r="F21" s="3">
-        <v>-987000</v>
+        <v>-783000</v>
       </c>
       <c r="G21" s="3">
+        <v>-804000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-920000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-348000</v>
-      </c>
       <c r="I21" s="3">
-        <v>-625000</v>
+        <v>-449000</v>
       </c>
       <c r="J21" s="3">
+        <v>-442000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-726000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1112000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1202000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1182000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1059000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1246000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1491000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1525000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1524000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1453000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2326000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1183000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1809,234 +1845,243 @@
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E22" s="3">
         <v>65000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>64000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>69000</v>
       </c>
       <c r="G22" s="3">
         <v>69000</v>
       </c>
       <c r="H22" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I22" s="3">
         <v>72000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>81000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>87000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>75000</v>
       </c>
       <c r="L22" s="3">
         <v>75000</v>
       </c>
       <c r="M22" s="3">
+        <v>75000</v>
+      </c>
+      <c r="N22" s="3">
         <v>73000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>55000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>54000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>33000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>24000</v>
       </c>
       <c r="S22" s="3">
         <v>24000</v>
       </c>
       <c r="T22" s="3">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="U22" s="3">
         <v>22000</v>
       </c>
       <c r="V22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="W22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>2000</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
+      <c r="AA22" s="3">
+        <v>2000</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-838000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-418000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-801000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1167000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1113000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-539000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-740000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1456000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1445000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1195000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1348000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1723000</v>
       </c>
       <c r="R23" s="3">
         <v>-1723000</v>
       </c>
       <c r="S23" s="3">
+        <v>-1723000</v>
+      </c>
+      <c r="T23" s="3">
         <v>-1709000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1593000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2461000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-580000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-414000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-353000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-200000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2000</v>
       </c>
       <c r="H24" s="3">
         <v>2000</v>
       </c>
       <c r="I24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1000</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>1000</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+        <v>1000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3000</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2067,8 +2112,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2153,180 +2201,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-837000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-416000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-804000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1166000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1115000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-541000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-743000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1457000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1446000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1195000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1349000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1723000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1724000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1712000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1593000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2461000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-580000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-414000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-353000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-833000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-416000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-811000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1117000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-545000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-744000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1457000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1446000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1195000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1349000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1723000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1724000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1712000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1593000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2461000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-580000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-414000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-354000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2411,8 +2468,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2497,8 +2557,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2583,8 +2646,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2669,37 +2735,40 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>478000</v>
+        <v>18000</v>
       </c>
       <c r="E32" s="3">
-        <v>32000</v>
+        <v>-28000</v>
       </c>
       <c r="F32" s="3">
-        <v>-191000</v>
+        <v>-151000</v>
       </c>
       <c r="G32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
-        <v>107000</v>
-      </c>
       <c r="I32" s="3">
-        <v>-182000</v>
+        <v>6000</v>
       </c>
       <c r="J32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K32" s="3">
         <v>184000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2000</v>
       </c>
       <c r="M32" s="3">
         <v>2000</v>
@@ -2708,32 +2777,32 @@
         <v>2000</v>
       </c>
       <c r="O32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-105000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-75000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-23000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2749,100 +2818,106 @@
       <c r="AB32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-833000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-416000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-811000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1117000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-545000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-744000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1457000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1446000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1195000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1349000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1723000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1724000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1712000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1593000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2461000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-580000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-414000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-354000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2927,185 +3002,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-833000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-416000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-811000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1117000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-545000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-744000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1457000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1446000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1195000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1349000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1723000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1724000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1712000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1593000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2461000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-580000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-414000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-354000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3136,8 +3220,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3168,74 +3253,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3592000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2845000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3579000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4441000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4812000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4693000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5294000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5396000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5763000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5979000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7857000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7941000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9260000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11244000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11568000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13272000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14923000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16432000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18133000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5156000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3658000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3254,52 +3340,55 @@
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1718000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1985000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2503000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2647000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2696000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2485000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2406000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1343000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2104000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1879000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1511000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1192000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>942000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
@@ -3313,8 +3402,8 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3340,68 +3429,71 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E43" s="3">
         <v>342000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>555000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>203000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>254000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>412000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>443000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>217000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>249000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>389000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>161000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>237000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>342000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>157000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>102000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>106000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>62000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3414,8 +3506,8 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3426,71 +3518,74 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1661000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1543000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1594000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1638000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2103000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2589000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2248000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2680000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2583000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2797000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2620000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2530000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2161000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1823000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1348000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>949000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>655000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>494000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>274000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>126000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3506,80 +3601,83 @@
       <c r="AB44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E45" s="3">
         <v>330000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>361000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>346000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>255000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>215000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>192000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>201000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>258000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>270000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>164000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>186000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>156000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>126000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>112000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>97000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>92000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>98000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>126000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>63000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>201000</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3598,74 +3696,77 @@
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7618000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7045000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8592000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9275000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10120000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10394000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10583000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9837000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10957000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11314000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12313000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12086000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12861000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13350000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13130000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14424000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15732000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17046000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18559000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5345000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3859000</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3684,17 +3785,20 @@
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E47" s="3">
         <v>669000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3728,8 +3832,8 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3770,74 +3874,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6265000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6035000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5690000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5389000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4914000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4565000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4381000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4216000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4188000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4209000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4230000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4155000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4186000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4151000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4088000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3959000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3812000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3666000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3411000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3051000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2541000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3856,8 +3963,11 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3942,8 +4052,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4028,8 +4141,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4114,74 +4230,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>560000</v>
+      </c>
+      <c r="E52" s="3">
         <v>484000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>582000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>553000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>563000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>546000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>446000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>209000</v>
       </c>
       <c r="K52" s="3">
         <v>209000</v>
       </c>
       <c r="L52" s="3">
+        <v>209000</v>
+      </c>
+      <c r="M52" s="3">
         <v>211000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>235000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>215000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>180000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>690000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>658000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>640000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>627000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>585000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>324000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>92000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>91000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4200,8 +4319,11 @@
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4286,74 +4408,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15140000</v>
+      </c>
+      <c r="E54" s="3">
         <v>14233000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14864000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15217000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15597000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15505000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15410000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14262000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15354000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15734000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16778000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16456000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17227000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18191000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17876000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19023000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20171000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21297000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22294000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8488000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6491000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4372,8 +4497,11 @@
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4404,8 +4532,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4436,74 +4565,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>889000</v>
+      </c>
+      <c r="E57" s="3">
         <v>754000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>595000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>554000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>489000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>713000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>499000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>617000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>769000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1019000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>981000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1134000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1007000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>984000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>828000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>732000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>571000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>483000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>417000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>203000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4522,53 +4652,56 @@
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E58" s="3">
         <v>114000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>113000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>233000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>100000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>215000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>253000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>205000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>88000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>207000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>200000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>193000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4585,11 +4718,11 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>1000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4608,74 +4741,77 @@
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1974000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1957000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2316000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1898000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1807000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1446000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1233000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>474000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>417000</v>
       </c>
       <c r="L59" s="3">
         <v>417000</v>
       </c>
       <c r="M59" s="3">
+        <v>417000</v>
+      </c>
+      <c r="N59" s="3">
         <v>536000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>442000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>358000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>343000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1424000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1281000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1021000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>953000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>830000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>630000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>615000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4694,74 +4830,77 @@
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3620000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3353000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3693000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3425000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2943000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2788000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2251000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1933000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2086000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2401000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2487000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2624000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2274000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2269000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2424000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2109000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1753000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1524000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1313000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1047000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>819000</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4780,74 +4919,77 @@
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5236000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5119000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5082000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4967000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4898000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4869000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4905000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5829000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5877000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4778000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4831000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3039000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3023000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3019000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1231000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1229000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1228000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1227000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1226000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2958000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4866,74 +5008,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E62" s="3">
         <v>448000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>429000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>457000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>449000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>454000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>404000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>414000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>396000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>328000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>186000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>132000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>138000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>103000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>422000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>348000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>322000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>286000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>241000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>195900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>151000</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4952,8 +5097,11 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5038,8 +5186,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5124,8 +5275,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5210,74 +5364,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10013000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9804000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10270000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10133000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9518000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9275000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8848000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8363000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8536000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7665000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7637000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5904000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5513000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5449000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4077000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3686000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3303000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3037000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2780000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4200900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>972000</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5296,8 +5453,11 @@
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5328,8 +5488,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5414,8 +5575,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5500,8 +5664,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5560,13 +5727,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>7894000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>7894000</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>7894000</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5586,8 +5753,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5672,74 +5842,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28200000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27367000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-26951000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-26140000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-24967000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-23850000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-23305000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22561000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-21461000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20004000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18558000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17037000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15670000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14475000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-13126000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11403000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9679000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7967000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6374000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3913000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2680000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5758,8 +5931,11 @@
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5844,8 +6020,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5930,8 +6109,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6016,74 +6198,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5106000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4403000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4566000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5066000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6068000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6222000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6558000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5899000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6818000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8069000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9141000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10552000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11714000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12742000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13799000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15337000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16868000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18260000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19514000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-3606900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-2375000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6102,8 +6287,11 @@
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6188,185 +6376,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-833000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-416000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-811000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1117000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-545000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-744000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1457000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1446000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1367000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1195000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1349000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1723000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1724000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1712000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1593000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2461000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-580000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-414000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-354000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6397,83 +6594,84 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E83" s="3">
         <v>200000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>218000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>259000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>274000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>280000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>270000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>256000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>223000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>188000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>199000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>174000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>161000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>118000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>199000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>174000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>161000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>118000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>113000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49000</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3">
         <v>17000</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>4</v>
       </c>
@@ -6483,8 +6681,11 @@
       <c r="AD83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6569,8 +6770,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6655,8 +6859,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6741,8 +6948,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6827,8 +7037,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6913,83 +7126,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-487000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-703000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-681000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>26000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>64000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-188000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1183000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-876000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-754000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1269000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1107000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-877000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1361000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1521000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1368000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1204000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1034000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1086000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-685000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-580000</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>4</v>
       </c>
@@ -6999,8 +7215,11 @@
       <c r="AD89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7031,83 +7250,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-362000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-372000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-463000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-447000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-462000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-338000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-327000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-277000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-283000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-254000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-298000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-190000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-255000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-283000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-294000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-298000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-359000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-418000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-455000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-469000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-605000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
@@ -7117,8 +7337,11 @@
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7203,8 +7426,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7289,83 +7515,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-321000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-393000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-706000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-408000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>501000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-489000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-606000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-603000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-432000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1193000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-283000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-294000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-298000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-359000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-418000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-456000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-467000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-604000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
@@ -7375,8 +7604,11 @@
       <c r="AD94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7407,8 +7639,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7451,8 +7684,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7493,8 +7726,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7579,8 +7815,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7665,8 +7904,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7751,83 +7993,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>139000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>756000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>104000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1030000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1621000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>32000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1485000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>37000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>56000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>14760000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2500000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2500000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
@@ -7837,59 +8082,62 @@
       <c r="AD100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
@@ -7905,8 +8153,8 @@
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7923,83 +8171,86 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-734000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-862000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-371000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>119000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-601000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-102000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-367000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-216000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1878000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-84000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1319000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-319000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1701000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1663000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1508000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1452000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13218000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1348000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3">
         <v>1316000</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
@@ -8007,6 +8258,9 @@
         <v>4</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
